--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484106_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484106_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.6036</v>
+        <v>1.4939</v>
       </c>
       <c r="E2" t="n">
-        <v>1.3393</v>
+        <v>1.0333</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2642</v>
+        <v>0.4606</v>
       </c>
       <c r="G2" t="n">
         <v>0.3726</v>
@@ -610,13 +610,13 @@
         <v>0.7935</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0289</v>
+        <v>-0.0808</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3061</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2772</v>
+        <v>-0.0808</v>
       </c>
       <c r="V2" t="n">
         <v>0.4085</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. AMABILINO PEREZ</t>
+          <t>A. PILAN PERET</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5337</v>
+        <v>1.1988</v>
       </c>
       <c r="E3" t="n">
-        <v>3.8893</v>
+        <v>1.4714</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.3556</v>
+        <v>-0.2725</v>
       </c>
       <c r="G3" t="n">
-        <v>-5.5753</v>
+        <v>1.9696</v>
       </c>
       <c r="H3" t="n">
-        <v>-3.3664</v>
+        <v>0.2918</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.2089</v>
+        <v>1.6777</v>
       </c>
       <c r="J3" t="n">
-        <v>-2.867</v>
+        <v>2.6009</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.0272</v>
+        <v>1.3508</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.8398</v>
+        <v>1.2501</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.7083</v>
+        <v>-0.6314</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.3392</v>
+        <v>-1.059</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3691</v>
+        <v>0.4276</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-1.5871</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1903</v>
+        <v>-3.1741</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1903</v>
+        <v>1.5871</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6473</v>
+        <v>-1.3306</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1758</v>
+        <v>-0.3684</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4714</v>
+        <v>-0.9623</v>
       </c>
       <c r="V3" t="n">
-        <v>6.4617</v>
+        <v>2.1469</v>
       </c>
       <c r="W3" t="n">
-        <v>7.7707</v>
+        <v>2.4129</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.309</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. PILAN PERET</t>
+          <t>A. AMABILINO PEREZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6278</v>
+        <v>0.7617</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0406</v>
+        <v>3.5662</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4128</v>
+        <v>-2.8044</v>
       </c>
       <c r="G4" t="n">
-        <v>1.9696</v>
+        <v>-5.5753</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2918</v>
+        <v>-3.3664</v>
       </c>
       <c r="I4" t="n">
-        <v>1.6777</v>
+        <v>-2.2089</v>
       </c>
       <c r="J4" t="n">
-        <v>2.6009</v>
+        <v>-2.867</v>
       </c>
       <c r="K4" t="n">
-        <v>1.3508</v>
+        <v>-1.0272</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2501</v>
+        <v>-1.8398</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.6314</v>
+        <v>-2.7083</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.059</v>
+        <v>-2.3392</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4276</v>
+        <v>-0.3691</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.5871</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.1741</v>
+        <v>-1.1903</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5871</v>
+        <v>1.1903</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.9017</v>
+        <v>-0.1247</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7991</v>
+        <v>-0.1473</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.1025</v>
+        <v>0.0226</v>
       </c>
       <c r="V4" t="n">
-        <v>2.1469</v>
+        <v>6.4617</v>
       </c>
       <c r="W4" t="n">
-        <v>2.4129</v>
+        <v>7.7707</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.266</v>
+        <v>-1.309</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E. GANDOL COBO</t>
+          <t>A. NEALE GIMENEZ-CASSINA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4238</v>
+        <v>0.4549</v>
       </c>
       <c r="E5" t="n">
-        <v>1.03</v>
+        <v>-0.1247</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6062</v>
+        <v>0.5796</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5588</v>
+        <v>0.4081</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3022</v>
+        <v>0.136</v>
       </c>
       <c r="I5" t="n">
-        <v>1.2566</v>
+        <v>0.2721</v>
       </c>
       <c r="J5" t="n">
-        <v>1.5377</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2876</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2501</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0212</v>
+        <v>0.4081</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0147</v>
+        <v>0.136</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0065</v>
+        <v>0.2721</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3968</v>
+        <v>0.1984</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3887</v>
+        <v>0.1984</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3253</v>
+        <v>-0.1516</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1189</v>
+        <v>-0.1247</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2064</v>
+        <v>-0.0269</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.2065</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.6032</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.8097</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. NEALE GIMENEZ-CASSINA</t>
+          <t>E. GANDOL COBO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3645</v>
+        <v>0.2985</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.187</v>
+        <v>0.8486</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5515</v>
+        <v>-0.5501</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4081</v>
+        <v>1.5588</v>
       </c>
       <c r="H6" t="n">
-        <v>0.136</v>
+        <v>0.3022</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2721</v>
+        <v>1.2566</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1.5377</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>0.2876</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.2501</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4081</v>
+        <v>0.0212</v>
       </c>
       <c r="N6" t="n">
-        <v>0.136</v>
+        <v>0.0147</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2721</v>
+        <v>0.0065</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1984</v>
+        <v>0.3968</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1984</v>
+        <v>1.3887</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.242</v>
+        <v>-0.4506</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.187</v>
+        <v>-0.3003</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.055</v>
+        <v>-0.1503</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.6032</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.8097</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.0279</v>
+        <v>-0.759</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.2535</v>
+        <v>-1.2932</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2255</v>
+        <v>0.5342</v>
       </c>
       <c r="G7" t="n">
         <v>-1.3659</v>
@@ -1000,13 +1000,13 @@
         <v>1.1903</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6784</v>
+        <v>-0.4095</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0566</v>
+        <v>-0.0963</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6218</v>
+        <v>-0.3132</v>
       </c>
       <c r="V7" t="n">
         <v>-0.1738</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. BONAZEBI LOUSSAKOU</t>
+          <t>D. IRUELA RUBIO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.7246</v>
+        <v>-1.1499</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4051</v>
+        <v>-1.08</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.1297</v>
+        <v>-0.0699</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.6587</v>
+        <v>-1.3601</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.1743</v>
+        <v>-2.4546</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4845</v>
+        <v>1.0946</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6751</v>
+        <v>0.3596</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.7151999999999999</v>
+        <v>-1.2596</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0402</v>
+        <v>1.6192</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.9837</v>
+        <v>-1.7197</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.459</v>
+        <v>-1.195</v>
       </c>
       <c r="O8" t="n">
         <v>-0.5247000000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.5952</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1903</v>
+        <v>-0.9919</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5952</v>
+        <v>0.9919</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4059</v>
+        <v>-0.2905</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6746</v>
+        <v>-0.4477</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2687</v>
+        <v>0.1572</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1234</v>
+        <v>0.5007</v>
       </c>
       <c r="W8" t="n">
-        <v>1.5959</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.4724</v>
+        <v>0.5007</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. IRUELA RUBIO</t>
+          <t>C. BONAZEBI LOUSSAKOU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.0208</v>
+        <v>-2.1163</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7545</v>
+        <v>-0.0427</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2663</v>
+        <v>-2.0736</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.3601</v>
+        <v>-1.6587</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.4546</v>
+        <v>-1.1743</v>
       </c>
       <c r="I9" t="n">
-        <v>1.0946</v>
+        <v>-0.4845</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3596</v>
+        <v>-0.6751</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.2596</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>1.6192</v>
+        <v>0.0402</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.7197</v>
+        <v>-0.9837</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.195</v>
+        <v>-0.459</v>
       </c>
       <c r="O9" t="n">
         <v>-0.5247000000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-0.5952</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9919</v>
+        <v>-1.1903</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9919</v>
+        <v>0.5952</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.1614</v>
+        <v>0.0142</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.1222</v>
+        <v>0.2268</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0392</v>
+        <v>-0.2126</v>
       </c>
       <c r="V9" t="n">
-        <v>0.5007</v>
+        <v>0.1234</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.5959</v>
       </c>
       <c r="X9" t="n">
-        <v>0.5007</v>
+        <v>-1.4724</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.1856</v>
+        <v>-2.8694</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5767</v>
+        <v>0.7806999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.7623</v>
+        <v>-3.6501</v>
       </c>
       <c r="G10" t="n">
         <v>0.7618</v>
@@ -1234,13 +1234,13 @@
         <v>0.3968</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9908</v>
+        <v>-0.6745</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4251</v>
+        <v>-0.221</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5657</v>
+        <v>-0.4535</v>
       </c>
       <c r="V10" t="n">
         <v>-3.3534</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.8279</v>
+        <v>-4.8216</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0426</v>
+        <v>0.1049</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.8704</v>
+        <v>-4.9265</v>
       </c>
       <c r="G11" t="n">
         <v>1.0415</v>
@@ -1312,13 +1312,13 @@
         <v>1.5871</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.103</v>
+        <v>-1.0968</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3683</v>
+        <v>-0.306</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7347</v>
+        <v>-0.7907999999999999</v>
       </c>
       <c r="V11" t="n">
         <v>-5.1631</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.9555</v>
+        <v>-4.845</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.3227</v>
+        <v>-1.9316</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.6328</v>
+        <v>-2.9134</v>
       </c>
       <c r="G12" t="n">
         <v>-0.5901</v>
@@ -1390,13 +1390,13 @@
         <v>1.3887</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.077</v>
+        <v>-0.9664</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0031</v>
+        <v>-0.612</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0738</v>
+        <v>-0.3544</v>
       </c>
       <c r="V12" t="n">
         <v>-0.5111</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.0293</v>
+        <v>-5.9298</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.3251</v>
+        <v>-2.917</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.7042</v>
+        <v>-3.0128</v>
       </c>
       <c r="G13" t="n">
         <v>-0.3071</v>
@@ -1468,13 +1468,13 @@
         <v>1.5871</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8576</v>
+        <v>-0.7581</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8728</v>
+        <v>-0.4647</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0152</v>
+        <v>-0.2934</v>
       </c>
       <c r="V13" t="n">
         <v>-4.4677</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-19.2182</v>
+        <v>-18.2832</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.5192000000000005</v>
+        <v>0.4158999999999993</v>
       </c>
       <c r="F14" t="n">
-        <v>-18.6991</v>
+        <v>-18.6989</v>
       </c>
       <c r="G14" t="n">
         <v>-4.7448</v>
@@ -1525,7 +1525,7 @@
         <v>1.2138</v>
       </c>
       <c r="L14" t="n">
-        <v>4.436199999999999</v>
+        <v>4.4362</v>
       </c>
       <c r="M14" t="n">
         <v>-10.3951</v>
@@ -1534,7 +1534,7 @@
         <v>-10.59</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1950999999999999</v>
+        <v>0.1951</v>
       </c>
       <c r="P14" t="n">
         <v>-1.9839</v>
@@ -1546,10 +1546,10 @@
         <v>12.8951</v>
       </c>
       <c r="S14" t="n">
-        <v>-7.255099999999999</v>
+        <v>-6.3199</v>
       </c>
       <c r="T14" t="n">
-        <v>-3.7966</v>
+        <v>-2.8616</v>
       </c>
       <c r="U14" t="n">
         <v>-3.4584</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>9.1374</v>
+        <v>8.180899999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>7.2741</v>
+        <v>6.4578</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8633</v>
+        <v>1.723</v>
       </c>
       <c r="G15" t="n">
         <v>3.6572</v>
@@ -1624,13 +1624,13 @@
         <v>2.1822</v>
       </c>
       <c r="S15" t="n">
-        <v>1.7543</v>
+        <v>0.7978</v>
       </c>
       <c r="T15" t="n">
-        <v>1.0544</v>
+        <v>0.2382</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6999</v>
+        <v>0.5596</v>
       </c>
       <c r="V15" t="n">
         <v>1.5437</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.6113</v>
+        <v>5.5151</v>
       </c>
       <c r="E16" t="n">
-        <v>2.9556</v>
+        <v>3.9759</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6557</v>
+        <v>1.5392</v>
       </c>
       <c r="G16" t="n">
         <v>4.5776</v>
@@ -1702,13 +1702,13 @@
         <v>1.9838</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.089</v>
+        <v>0.8148</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8615</v>
+        <v>0.1588</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7724</v>
+        <v>0.656</v>
       </c>
       <c r="V16" t="n">
         <v>-0.8692</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.8913</v>
+        <v>3.6396</v>
       </c>
       <c r="E17" t="n">
-        <v>4.9788</v>
+        <v>4.3666</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.0875</v>
+        <v>-0.727</v>
       </c>
       <c r="G17" t="n">
         <v>3.5268</v>
@@ -1780,13 +1780,13 @@
         <v>1.1903</v>
       </c>
       <c r="S17" t="n">
-        <v>1.3116</v>
+        <v>1.0599</v>
       </c>
       <c r="T17" t="n">
-        <v>1.3548</v>
+        <v>0.7426</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0432</v>
+        <v>0.3173</v>
       </c>
       <c r="V17" t="n">
         <v>3.8141</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X. ELVIRA GOMEZ</t>
+          <t>V. VINÓS ALTEMIR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.9701</v>
+        <v>3.0746</v>
       </c>
       <c r="E18" t="n">
-        <v>3.7391</v>
+        <v>1.5253</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.769</v>
+        <v>1.5493</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4486</v>
+        <v>1.5343</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4686</v>
+        <v>0.6352</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.9172</v>
+        <v>0.8991</v>
       </c>
       <c r="J18" t="n">
-        <v>0.114</v>
+        <v>2.1657</v>
       </c>
       <c r="K18" t="n">
-        <v>0.7916</v>
+        <v>0.3533</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6776</v>
+        <v>1.8124</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5626</v>
+        <v>-0.6314</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.323</v>
+        <v>0.2818</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2396</v>
+        <v>-0.9133</v>
       </c>
       <c r="P18" t="n">
-        <v>1.3887</v>
+        <v>0.3968</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R18" t="n">
         <v>1.3887</v>
       </c>
       <c r="S18" t="n">
-        <v>1.8353</v>
+        <v>1.1435</v>
       </c>
       <c r="T18" t="n">
-        <v>1.3548</v>
+        <v>0.3515</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4805</v>
+        <v>0.792</v>
       </c>
       <c r="V18" t="n">
-        <v>0.1947</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>2.2704</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.0757</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>V. VINÓS ALTEMIR</t>
+          <t>X. ELVIRA GOMEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.6707</v>
+        <v>1.9396</v>
       </c>
       <c r="E19" t="n">
-        <v>1.1172</v>
+        <v>2.8209</v>
       </c>
       <c r="F19" t="n">
-        <v>1.5535</v>
+        <v>-0.8812</v>
       </c>
       <c r="G19" t="n">
-        <v>1.5343</v>
+        <v>-0.4486</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6352</v>
+        <v>0.4686</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8991</v>
+        <v>-0.9172</v>
       </c>
       <c r="J19" t="n">
-        <v>2.1657</v>
+        <v>0.114</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3533</v>
+        <v>0.7916</v>
       </c>
       <c r="L19" t="n">
-        <v>1.8124</v>
+        <v>-0.6776</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.6314</v>
+        <v>-0.5626</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2818</v>
+        <v>-0.323</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.9133</v>
+        <v>-0.2396</v>
       </c>
       <c r="P19" t="n">
-        <v>0.3968</v>
+        <v>1.3887</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>1.3887</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7397</v>
+        <v>0.8048</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0566</v>
+        <v>0.4365</v>
       </c>
       <c r="U19" t="n">
-        <v>0.7963</v>
+        <v>0.3683</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.1947</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.2704</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-2.0757</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E. IBAEZ ALDAZABAL</t>
+          <t>R. RIU GARCIA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.9961</v>
+        <v>1.4185</v>
       </c>
       <c r="E20" t="n">
-        <v>0.008399999999999999</v>
+        <v>1.0643</v>
       </c>
       <c r="F20" t="n">
-        <v>1.9878</v>
+        <v>0.3542</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.6183</v>
+        <v>-1.4016</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.8056</v>
+        <v>-0.4688</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.8127</v>
+        <v>-0.9328</v>
       </c>
       <c r="J20" t="n">
-        <v>-3.0574</v>
+        <v>-0.9572000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.0219</v>
+        <v>-0.277</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.0355</v>
+        <v>-0.6802</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.5610000000000001</v>
+        <v>-0.4444</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2163</v>
+        <v>-0.1918</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.7772</v>
+        <v>-0.2526</v>
       </c>
       <c r="P20" t="n">
-        <v>1.7855</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R20" t="n">
-        <v>1.7855</v>
+        <v>0.9919</v>
       </c>
       <c r="S20" t="n">
-        <v>2.214</v>
+        <v>0.3359</v>
       </c>
       <c r="T20" t="n">
-        <v>1.8593</v>
+        <v>0.3345</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3547</v>
+        <v>0.0014</v>
       </c>
       <c r="V20" t="n">
-        <v>1.615</v>
+        <v>2.4842</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2065</v>
+        <v>2.6789</v>
       </c>
       <c r="X20" t="n">
-        <v>0.4085</v>
+        <v>-0.1947</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.6551</v>
+        <v>1.3185</v>
       </c>
       <c r="E21" t="n">
         <v>1.992</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3369</v>
+        <v>-0.6736</v>
       </c>
       <c r="G21" t="n">
         <v>0.9661999999999999</v>
@@ -2092,13 +2092,13 @@
         <v>1.1903</v>
       </c>
       <c r="S21" t="n">
-        <v>1.0225</v>
+        <v>0.6858</v>
       </c>
       <c r="T21" t="n">
         <v>0.2438</v>
       </c>
       <c r="U21" t="n">
-        <v>0.7786999999999999</v>
+        <v>0.442</v>
       </c>
       <c r="V21" t="n">
         <v>-0.532</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R. RIU GARCIA</t>
+          <t>M. VIEYTES VERDU</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9381</v>
+        <v>1.2768</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8603</v>
+        <v>0.6105</v>
       </c>
       <c r="F22" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.6663</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.4016</v>
+        <v>0.4446</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.4688</v>
+        <v>2.0667</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.9328</v>
+        <v>-1.622</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.9572000000000001</v>
+        <v>0.9481000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.277</v>
+        <v>2.1881</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6802</v>
+        <v>-1.2399</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.4444</v>
+        <v>-0.5034999999999999</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.1918</v>
+        <v>-0.1214</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2526</v>
+        <v>-0.3821</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>0.3968</v>
       </c>
       <c r="Q22" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9919</v>
+        <v>1.3887</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1445</v>
+        <v>0.3642</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1304</v>
+        <v>0.0511</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.275</v>
+        <v>0.3131</v>
       </c>
       <c r="V22" t="n">
-        <v>2.4842</v>
+        <v>0.0713</v>
       </c>
       <c r="W22" t="n">
-        <v>2.6789</v>
+        <v>0.6032</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.1947</v>
+        <v>-0.532</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. VIEYTES VERDU</t>
+          <t>E. IBAEZ ALDAZABAL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.4122</v>
+        <v>1.27</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.0016</v>
+        <v>-0.9099</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4138</v>
+        <v>2.1799</v>
       </c>
       <c r="G23" t="n">
-        <v>0.4446</v>
+        <v>-3.6183</v>
       </c>
       <c r="H23" t="n">
-        <v>2.0667</v>
+        <v>-0.8056</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.622</v>
+        <v>-2.8127</v>
       </c>
       <c r="J23" t="n">
-        <v>0.9481000000000001</v>
+        <v>-3.0574</v>
       </c>
       <c r="K23" t="n">
-        <v>2.1881</v>
+        <v>-1.0219</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.2399</v>
+        <v>-2.0355</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.5034999999999999</v>
+        <v>-0.5610000000000001</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.1214</v>
+        <v>0.2163</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.3821</v>
+        <v>-0.7772</v>
       </c>
       <c r="P23" t="n">
-        <v>0.3968</v>
+        <v>1.7855</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3887</v>
+        <v>1.7855</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5004999999999999</v>
+        <v>1.4879</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5611</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0606</v>
+        <v>0.5469000000000001</v>
       </c>
       <c r="V23" t="n">
-        <v>0.0713</v>
+        <v>1.615</v>
       </c>
       <c r="W23" t="n">
-        <v>0.6032</v>
+        <v>1.2065</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.532</v>
+        <v>0.4085</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.6462</v>
+        <v>-2.154</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.1324</v>
+        <v>0.2757</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.5138</v>
+        <v>-2.4297</v>
       </c>
       <c r="G24" t="n">
         <v>-0.4983</v>
@@ -2326,13 +2326,13 @@
         <v>0.7935</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.06859999999999999</v>
+        <v>0.4237</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4988</v>
+        <v>-0.0906</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4302</v>
+        <v>0.5143</v>
       </c>
       <c r="V24" t="n">
         <v>-1.881</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.4179</v>
+        <v>-5.5813</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.0924</v>
+        <v>-3.4802</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.3256</v>
+        <v>-2.1011</v>
       </c>
       <c r="G25" t="n">
         <v>-3.9951</v>
@@ -2404,13 +2404,13 @@
         <v>0.5952</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.8196</v>
+        <v>0.017</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.5611</v>
+        <v>0.0511</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2585</v>
+        <v>-0.034</v>
       </c>
       <c r="V25" t="n">
         <v>-1.2065</v>
@@ -2437,22 +2437,22 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>19.2182</v>
+        <v>19.8983</v>
       </c>
       <c r="E26" t="n">
-        <v>18.6991</v>
+        <v>18.6989</v>
       </c>
       <c r="F26" t="n">
-        <v>0.5191000000000003</v>
+        <v>1.1993</v>
       </c>
       <c r="G26" t="n">
         <v>4.744800000000001</v>
       </c>
       <c r="H26" t="n">
-        <v>9.376399999999999</v>
+        <v>9.3764</v>
       </c>
       <c r="I26" t="n">
-        <v>-4.6315</v>
+        <v>-4.631500000000001</v>
       </c>
       <c r="J26" t="n">
         <v>10.3949</v>
@@ -2461,7 +2461,7 @@
         <v>10.5901</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.1950999999999994</v>
+        <v>-0.1950999999999998</v>
       </c>
       <c r="M26" t="n">
         <v>-5.6501</v>
@@ -2482,13 +2482,13 @@
         <v>14.8788</v>
       </c>
       <c r="S26" t="n">
-        <v>7.255199999999999</v>
+        <v>7.935300000000001</v>
       </c>
       <c r="T26" t="n">
-        <v>3.4584</v>
+        <v>3.4585</v>
       </c>
       <c r="U26" t="n">
-        <v>3.7966</v>
+        <v>4.476900000000001</v>
       </c>
       <c r="V26" t="n">
         <v>5.234299999999999</v>
